--- a/docs/exemple-livrable/Microplan_Antsirabe_II.xlsx
+++ b/docs/exemple-livrable/Microplan_Antsirabe_II.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Communes'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fokontany'!$A$1:$K$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fokontany'!$A$1:$L$205</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Équipes'!$A$1:$H$227</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Calendrier'!$A$1:$E$912</definedName>
   </definedNames>
@@ -554,7 +554,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Population 2018 calée et 2026 WorldPop, écart, cible, formation sanitaire la plus proche</t>
+          <t>Population 2018 calée et WorldPop (écart entre les deux), population 2026, cible, formation sanitaire la plus proche</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -729,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -960,7 +960,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1125,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1191,7 +1191,7 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1257,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1290,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1323,7 +1323,7 @@
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1338,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1346,12 +1346,13 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1377,35 +1378,40 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>Population 2018 WorldPop</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Écart 2018 (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Population 2026 WorldPop</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Écart (%)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>À vérifier</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Cible</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Jours-équipe</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Formation sanitaire la plus proche</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Distance (km, vol d'oiseau)</t>
         </is>
@@ -1431,28 +1437,27 @@
         <v>9436</v>
       </c>
       <c r="E2" t="n">
+        <v>11295</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>13279</v>
       </c>
-      <c r="F2" t="n">
-        <v>41</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>2257</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>18.8</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -1476,28 +1481,31 @@
         <v>4723</v>
       </c>
       <c r="E3" t="n">
+        <v>8641</v>
+      </c>
+      <c r="F3" t="n">
+        <v>83</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>10297</v>
       </c>
-      <c r="F3" t="n">
-        <v>118</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1750</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>14.6</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1521,24 +1529,27 @@
         <v>6513</v>
       </c>
       <c r="E4" t="n">
-        <v>8261</v>
+        <v>6963</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
+        <v>8261</v>
+      </c>
+      <c r="I4" t="n">
         <v>1404</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>11.7</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Bemasoandro Health Post</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -1562,24 +1573,27 @@
         <v>5957</v>
       </c>
       <c r="E5" t="n">
-        <v>6154</v>
+        <v>5258</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
+        <v>6154</v>
+      </c>
+      <c r="I5" t="n">
         <v>1046</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>7.9</v>
       </c>
     </row>
@@ -1603,28 +1617,31 @@
         <v>2606</v>
       </c>
       <c r="E6" t="n">
+        <v>3562</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>4212</v>
       </c>
-      <c r="F6" t="n">
-        <v>62</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>716</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>6</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1648,24 +1665,27 @@
         <v>4419</v>
       </c>
       <c r="E7" t="n">
-        <v>4202</v>
+        <v>3495</v>
       </c>
       <c r="F7" t="n">
-        <v>-5</v>
+        <v>-21</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
+        <v>4202</v>
+      </c>
+      <c r="I7" t="n">
         <v>714</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Bemasoandro Health Post</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>9.6</v>
       </c>
     </row>
@@ -1689,24 +1709,27 @@
         <v>4495</v>
       </c>
       <c r="E8" t="n">
-        <v>4135</v>
+        <v>3475</v>
       </c>
       <c r="F8" t="n">
-        <v>-8</v>
+        <v>-23</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
+        <v>4135</v>
+      </c>
+      <c r="I8" t="n">
         <v>703</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5.9</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -1730,24 +1753,27 @@
         <v>2925</v>
       </c>
       <c r="E9" t="n">
-        <v>3778</v>
+        <v>3194</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
+        <v>3778</v>
+      </c>
+      <c r="I9" t="n">
         <v>642</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>5.3</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -1771,28 +1797,31 @@
         <v>4816</v>
       </c>
       <c r="E10" t="n">
+        <v>2543</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-47</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>2987</v>
       </c>
-      <c r="F10" t="n">
-        <v>-38</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>508</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4.2</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Bemasoandro Health Post</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>7.7</v>
       </c>
     </row>
@@ -1816,24 +1845,27 @@
         <v>2013</v>
       </c>
       <c r="E11" t="n">
-        <v>2109</v>
+        <v>1818</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
+        <v>2109</v>
+      </c>
+      <c r="I11" t="n">
         <v>359</v>
       </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -1857,28 +1889,31 @@
         <v>4342</v>
       </c>
       <c r="E12" t="n">
+        <v>1577</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-64</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>1862</v>
       </c>
-      <c r="F12" t="n">
-        <v>-57</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>317</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>2.6</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Marofangady Health Post</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>12.7</v>
       </c>
     </row>
@@ -1902,24 +1937,27 @@
         <v>1795</v>
       </c>
       <c r="E13" t="n">
-        <v>1641</v>
+        <v>1423</v>
       </c>
       <c r="F13" t="n">
-        <v>-9</v>
+        <v>-21</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
+        <v>1641</v>
+      </c>
+      <c r="I13" t="n">
         <v>279</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>2.3</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -1943,28 +1981,31 @@
         <v>3970</v>
       </c>
       <c r="E14" t="n">
+        <v>8386</v>
+      </c>
+      <c r="F14" t="n">
+        <v>111</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>10169</v>
       </c>
-      <c r="F14" t="n">
-        <v>156</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1729</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>14.4</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -1988,28 +2029,31 @@
         <v>2516</v>
       </c>
       <c r="E15" t="n">
+        <v>7176</v>
+      </c>
+      <c r="F15" t="n">
+        <v>185</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>8372</v>
       </c>
-      <c r="F15" t="n">
-        <v>233</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>1423</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11.9</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Andranomanelatra Health Centre</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -2033,28 +2077,31 @@
         <v>3791</v>
       </c>
       <c r="E16" t="n">
+        <v>6806</v>
+      </c>
+      <c r="F16" t="n">
+        <v>80</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>8119</v>
       </c>
-      <c r="F16" t="n">
-        <v>114</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>1380</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>11.5</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Andranomanelatra Health Centre</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2078,28 +2125,31 @@
         <v>2811</v>
       </c>
       <c r="E17" t="n">
+        <v>4481</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>5318</v>
       </c>
-      <c r="F17" t="n">
-        <v>89</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>904</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>7.5</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Andranomanelatra Health Centre</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -2123,28 +2173,31 @@
         <v>2792</v>
       </c>
       <c r="E18" t="n">
+        <v>4385</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>5194</v>
       </c>
-      <c r="F18" t="n">
-        <v>86</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>883</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>7.4</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Bemasoandro Health Post</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -2168,28 +2221,27 @@
         <v>3887</v>
       </c>
       <c r="E19" t="n">
+        <v>4338</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>5150</v>
       </c>
-      <c r="F19" t="n">
-        <v>32</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>876</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>7.3</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Ambohimiarivo Health Centre</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>4.8</v>
       </c>
     </row>
@@ -2213,28 +2265,31 @@
         <v>1944</v>
       </c>
       <c r="E20" t="n">
+        <v>3272</v>
+      </c>
+      <c r="F20" t="n">
+        <v>68</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>3916</v>
       </c>
-      <c r="F20" t="n">
-        <v>101</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>666</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5.5</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Andranomanelatra Health Centre</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -2258,28 +2313,27 @@
         <v>2576</v>
       </c>
       <c r="E21" t="n">
+        <v>3047</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>3578</v>
       </c>
-      <c r="F21" t="n">
-        <v>39</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>608</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5.1</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Bemasoandro Health Post</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2303,28 +2357,31 @@
         <v>1158</v>
       </c>
       <c r="E22" t="n">
+        <v>3002</v>
+      </c>
+      <c r="F22" t="n">
+        <v>159</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>3513</v>
       </c>
-      <c r="F22" t="n">
-        <v>203</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>597</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>5</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Andranomanelatra Health Centre</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -2348,24 +2405,27 @@
         <v>3141</v>
       </c>
       <c r="E23" t="n">
-        <v>3050</v>
+        <v>2584</v>
       </c>
       <c r="F23" t="n">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
+        <v>3050</v>
+      </c>
+      <c r="I23" t="n">
         <v>518</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>4.3</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Amberobe Health Centre</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -2389,24 +2449,31 @@
         <v>2433</v>
       </c>
       <c r="E24" t="n">
+        <v>1697</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>2010</v>
       </c>
-      <c r="F24" t="n">
-        <v>-17</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>342</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>2.9</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Ambohimiarivo Health Centre</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -2430,28 +2497,27 @@
         <v>1184</v>
       </c>
       <c r="E25" t="n">
+        <v>1413</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
         <v>1691</v>
       </c>
-      <c r="F25" t="n">
-        <v>43</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>287</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>2.4</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Andranomanelatra Health Centre</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2475,28 +2541,31 @@
         <v>921</v>
       </c>
       <c r="E26" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F26" t="n">
+        <v>53</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>1676</v>
       </c>
-      <c r="F26" t="n">
-        <v>82</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>285</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>2.4</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Amberobe Health Centre</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -2520,28 +2589,31 @@
         <v>1678</v>
       </c>
       <c r="E27" t="n">
+        <v>838</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>980</v>
       </c>
-      <c r="F27" t="n">
-        <v>-42</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>167</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1.4</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Ambohimiarivo Health Centre</t>
         </is>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -2565,28 +2637,31 @@
         <v>2721</v>
       </c>
       <c r="E28" t="n">
+        <v>3998</v>
+      </c>
+      <c r="F28" t="n">
+        <v>47</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>4660</v>
       </c>
-      <c r="F28" t="n">
-        <v>71</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>792</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>6.6</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -2610,28 +2685,27 @@
         <v>3469</v>
       </c>
       <c r="E29" t="n">
+        <v>3920</v>
+      </c>
+      <c r="F29" t="n">
+        <v>13</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
         <v>4547</v>
       </c>
-      <c r="F29" t="n">
-        <v>31</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>773</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>6.4</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -2655,24 +2729,27 @@
         <v>3478</v>
       </c>
       <c r="E30" t="n">
-        <v>4357</v>
+        <v>3764</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
+        <v>4357</v>
+      </c>
+      <c r="I30" t="n">
         <v>741</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>6.2</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>4.7</v>
       </c>
     </row>
@@ -2696,28 +2773,27 @@
         <v>2941</v>
       </c>
       <c r="E31" t="n">
+        <v>3499</v>
+      </c>
+      <c r="F31" t="n">
+        <v>19</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
         <v>4183</v>
       </c>
-      <c r="F31" t="n">
-        <v>42</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>711</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>5.9</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>11.6</v>
       </c>
     </row>
@@ -2741,28 +2817,31 @@
         <v>2318</v>
       </c>
       <c r="E32" t="n">
+        <v>3246</v>
+      </c>
+      <c r="F32" t="n">
+        <v>40</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>3842</v>
       </c>
-      <c r="F32" t="n">
-        <v>66</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>653</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>5.4</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -2786,28 +2865,31 @@
         <v>5233</v>
       </c>
       <c r="E33" t="n">
+        <v>2953</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>3505</v>
       </c>
-      <c r="F33" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>596</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>5</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -2831,28 +2913,31 @@
         <v>1923</v>
       </c>
       <c r="E34" t="n">
+        <v>2935</v>
+      </c>
+      <c r="F34" t="n">
+        <v>53</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
         <v>3413</v>
       </c>
-      <c r="F34" t="n">
-        <v>77</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>580</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>4.8</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2876,24 +2961,31 @@
         <v>4343</v>
       </c>
       <c r="E35" t="n">
+        <v>2941</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-32</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>3371</v>
       </c>
-      <c r="F35" t="n">
-        <v>-22</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>573</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>4.8</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>9.9</v>
       </c>
     </row>
@@ -2917,24 +3009,27 @@
         <v>2672</v>
       </c>
       <c r="E36" t="n">
-        <v>3216</v>
+        <v>2806</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
+        <v>3216</v>
+      </c>
+      <c r="I36" t="n">
         <v>547</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>4.6</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>9.6</v>
       </c>
     </row>
@@ -2958,24 +3053,27 @@
         <v>2255</v>
       </c>
       <c r="E37" t="n">
-        <v>2906</v>
+        <v>2529</v>
       </c>
       <c r="F37" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
+        <v>2906</v>
+      </c>
+      <c r="I37" t="n">
         <v>494</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>4.1</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -2999,24 +3097,27 @@
         <v>3068</v>
       </c>
       <c r="E38" t="n">
-        <v>2873</v>
+        <v>2449</v>
       </c>
       <c r="F38" t="n">
-        <v>-6</v>
+        <v>-20</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
+        <v>2873</v>
+      </c>
+      <c r="I38" t="n">
         <v>488</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>4.1</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3040,28 +3141,31 @@
         <v>1200</v>
       </c>
       <c r="E39" t="n">
+        <v>2372</v>
+      </c>
+      <c r="F39" t="n">
+        <v>98</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>2792</v>
       </c>
-      <c r="F39" t="n">
-        <v>133</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>475</v>
       </c>
-      <c r="I39" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3085,28 +3189,27 @@
         <v>1710</v>
       </c>
       <c r="E40" t="n">
+        <v>2090</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
         <v>2423</v>
       </c>
-      <c r="F40" t="n">
-        <v>42</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>412</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>3.4</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -3130,24 +3233,27 @@
         <v>1917</v>
       </c>
       <c r="E41" t="n">
-        <v>2169</v>
+        <v>1815</v>
       </c>
       <c r="F41" t="n">
-        <v>13</v>
+        <v>-5</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
+        <v>2169</v>
+      </c>
+      <c r="I41" t="n">
         <v>369</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>3.1</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Bemasoandro Health Post</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6.6</v>
       </c>
     </row>
@@ -3171,24 +3277,27 @@
         <v>1889</v>
       </c>
       <c r="E42" t="n">
-        <v>2119</v>
+        <v>1789</v>
       </c>
       <c r="F42" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
+        <v>2119</v>
+      </c>
+      <c r="I42" t="n">
         <v>360</v>
       </c>
-      <c r="I42" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3212,24 +3321,27 @@
         <v>2111</v>
       </c>
       <c r="E43" t="n">
-        <v>1961</v>
+        <v>1674</v>
       </c>
       <c r="F43" t="n">
-        <v>-7</v>
+        <v>-21</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
+        <v>1961</v>
+      </c>
+      <c r="I43" t="n">
         <v>333</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>2.8</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -3253,24 +3365,31 @@
         <v>2422</v>
       </c>
       <c r="E44" t="n">
+        <v>1593</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>1843</v>
       </c>
-      <c r="F44" t="n">
-        <v>-24</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>313</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>2.6</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -3294,24 +3413,31 @@
         <v>2207</v>
       </c>
       <c r="E45" t="n">
+        <v>1349</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-39</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
         <v>1619</v>
       </c>
-      <c r="F45" t="n">
-        <v>-27</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>275</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>2.3</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -3335,28 +3461,31 @@
         <v>726</v>
       </c>
       <c r="E46" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F46" t="n">
+        <v>80</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
         <v>1540</v>
       </c>
-      <c r="F46" t="n">
-        <v>112</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>262</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>2.2</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -3380,28 +3509,27 @@
         <v>4370</v>
       </c>
       <c r="E47" t="n">
+        <v>5524</v>
+      </c>
+      <c r="F47" t="n">
+        <v>26</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
         <v>6658</v>
       </c>
-      <c r="F47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>1132</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>9.4</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -3425,28 +3553,31 @@
         <v>2909</v>
       </c>
       <c r="E48" t="n">
+        <v>4789</v>
+      </c>
+      <c r="F48" t="n">
+        <v>65</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
         <v>5791</v>
       </c>
-      <c r="F48" t="n">
-        <v>99</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>984</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3470,28 +3601,27 @@
         <v>2568</v>
       </c>
       <c r="E49" t="n">
+        <v>2884</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
         <v>3429</v>
       </c>
-      <c r="F49" t="n">
-        <v>34</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>583</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>4.9</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -3515,28 +3645,31 @@
         <v>4655</v>
       </c>
       <c r="E50" t="n">
+        <v>2284</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
         <v>2749</v>
       </c>
-      <c r="F50" t="n">
-        <v>-41</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>467</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>3.9</v>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>8.6</v>
       </c>
     </row>
@@ -3560,28 +3693,31 @@
         <v>1141</v>
       </c>
       <c r="E51" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F51" t="n">
+        <v>88</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
         <v>2547</v>
       </c>
-      <c r="F51" t="n">
-        <v>123</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>433</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>3.6</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -3605,28 +3741,27 @@
         <v>1619</v>
       </c>
       <c r="E52" t="n">
+        <v>2083</v>
+      </c>
+      <c r="F52" t="n">
+        <v>29</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
         <v>2468</v>
       </c>
-      <c r="F52" t="n">
-        <v>52</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>420</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>3.5</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -3650,24 +3785,31 @@
         <v>3027</v>
       </c>
       <c r="E53" t="n">
+        <v>2069</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-32</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
         <v>2449</v>
       </c>
-      <c r="F53" t="n">
-        <v>-19</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>416</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>3.5</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>13.9</v>
       </c>
     </row>
@@ -3691,28 +3833,31 @@
         <v>1448</v>
       </c>
       <c r="E54" t="n">
+        <v>1942</v>
+      </c>
+      <c r="F54" t="n">
+        <v>34</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
         <v>2322</v>
       </c>
-      <c r="F54" t="n">
-        <v>60</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>395</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>3.3</v>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -3736,24 +3881,27 @@
         <v>1818</v>
       </c>
       <c r="E55" t="n">
-        <v>1806</v>
+        <v>1505</v>
       </c>
       <c r="F55" t="n">
-        <v>-1</v>
+        <v>-17</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
+        <v>1806</v>
+      </c>
+      <c r="I55" t="n">
         <v>307</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>2.6</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>11.4</v>
       </c>
     </row>
@@ -3777,24 +3925,27 @@
         <v>1967</v>
       </c>
       <c r="E56" t="n">
-        <v>1761</v>
+        <v>1472</v>
       </c>
       <c r="F56" t="n">
-        <v>-10</v>
+        <v>-25</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
+        <v>1761</v>
+      </c>
+      <c r="I56" t="n">
         <v>299</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>2.5</v>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>15.7</v>
       </c>
     </row>
@@ -3818,28 +3969,31 @@
         <v>1807</v>
       </c>
       <c r="E57" t="n">
+        <v>989</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-45</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
         <v>1204</v>
       </c>
-      <c r="F57" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>205</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>1.7</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -3863,24 +4017,27 @@
         <v>1070</v>
       </c>
       <c r="E58" t="n">
-        <v>1103</v>
+        <v>913</v>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>-15</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
+        <v>1103</v>
+      </c>
+      <c r="I58" t="n">
         <v>188</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>1.6</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>13.4</v>
       </c>
     </row>
@@ -3904,24 +4061,27 @@
         <v>1139</v>
       </c>
       <c r="E59" t="n">
-        <v>1037</v>
+        <v>869</v>
       </c>
       <c r="F59" t="n">
-        <v>-9</v>
+        <v>-24</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
+        <v>1037</v>
+      </c>
+      <c r="I59" t="n">
         <v>176</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>1.5</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -3945,28 +4105,31 @@
         <v>1275</v>
       </c>
       <c r="E60" t="n">
+        <v>666</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
         <v>806</v>
       </c>
-      <c r="F60" t="n">
-        <v>-37</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>137</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>1.1</v>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7.3</v>
       </c>
     </row>
@@ -3990,28 +4153,31 @@
         <v>1405</v>
       </c>
       <c r="E61" t="n">
+        <v>624</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-56</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
         <v>762</v>
       </c>
-      <c r="F61" t="n">
-        <v>-46</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>130</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>1.1</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>10.1</v>
       </c>
     </row>
@@ -4035,28 +4201,31 @@
         <v>1176</v>
       </c>
       <c r="E62" t="n">
+        <v>531</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
         <v>640</v>
       </c>
-      <c r="F62" t="n">
-        <v>-46</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>109</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>0.9</v>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>7.9</v>
       </c>
     </row>
@@ -4080,28 +4249,31 @@
         <v>3517</v>
       </c>
       <c r="E63" t="n">
+        <v>9843</v>
+      </c>
+      <c r="F63" t="n">
+        <v>180</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
         <v>11705</v>
       </c>
-      <c r="F63" t="n">
-        <v>233</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>1990</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>16.6</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -4125,28 +4297,31 @@
         <v>3840</v>
       </c>
       <c r="E64" t="n">
+        <v>6731</v>
+      </c>
+      <c r="F64" t="n">
+        <v>75</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
         <v>8090</v>
       </c>
-      <c r="F64" t="n">
-        <v>111</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>1375</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>11.5</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -4170,24 +4345,27 @@
         <v>2724</v>
       </c>
       <c r="E65" t="n">
-        <v>2938</v>
+        <v>2485</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>-9</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
+        <v>2938</v>
+      </c>
+      <c r="I65" t="n">
         <v>499</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>4.2</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Farihitsara Health Post</t>
         </is>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -4211,28 +4389,31 @@
         <v>1683</v>
       </c>
       <c r="E66" t="n">
+        <v>2224</v>
+      </c>
+      <c r="F66" t="n">
+        <v>32</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
         <v>2595</v>
       </c>
-      <c r="F66" t="n">
-        <v>54</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>441</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>3.7</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -4256,28 +4437,31 @@
         <v>1043</v>
       </c>
       <c r="E67" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F67" t="n">
+        <v>89</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
         <v>2339</v>
       </c>
-      <c r="F67" t="n">
-        <v>124</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>398</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>3.3</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -4301,28 +4485,27 @@
         <v>1485</v>
       </c>
       <c r="E68" t="n">
+        <v>1769</v>
+      </c>
+      <c r="F68" t="n">
+        <v>19</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
         <v>2139</v>
       </c>
-      <c r="F68" t="n">
-        <v>44</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>364</v>
       </c>
-      <c r="I68" t="n">
-        <v>3</v>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Fanjakamandroso Health Centre</t>
         </is>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -4346,24 +4529,27 @@
         <v>2215</v>
       </c>
       <c r="E69" t="n">
-        <v>1892</v>
+        <v>1570</v>
       </c>
       <c r="F69" t="n">
-        <v>-15</v>
+        <v>-29</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
+        <v>1892</v>
+      </c>
+      <c r="I69" t="n">
         <v>322</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>2.7</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Fanjakamandroso Health Centre</t>
         </is>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -4387,28 +4573,27 @@
         <v>1199</v>
       </c>
       <c r="E70" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
         <v>1582</v>
       </c>
-      <c r="F70" t="n">
-        <v>32</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>269</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>2.2</v>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Farihitsara Health Post</t>
         </is>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -4432,24 +4617,27 @@
         <v>1860</v>
       </c>
       <c r="E71" t="n">
-        <v>1572</v>
+        <v>1324</v>
       </c>
       <c r="F71" t="n">
-        <v>-15</v>
+        <v>-29</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
+        <v>1572</v>
+      </c>
+      <c r="I71" t="n">
         <v>267</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>2.2</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>9.699999999999999</v>
       </c>
     </row>
@@ -4473,28 +4661,31 @@
         <v>1842</v>
       </c>
       <c r="E72" t="n">
+        <v>1058</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-43</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
         <v>1235</v>
       </c>
-      <c r="F72" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>210</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>1.8</v>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Fanjakamandroso Health Centre</t>
         </is>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>6.2</v>
       </c>
     </row>
@@ -4518,24 +4709,27 @@
         <v>997</v>
       </c>
       <c r="E73" t="n">
-        <v>1232</v>
+        <v>1012</v>
       </c>
       <c r="F73" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
+        <v>1232</v>
+      </c>
+      <c r="I73" t="n">
         <v>209</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>1.7</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Sahanivotry Atsinanana Health Post</t>
         </is>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -4559,28 +4753,31 @@
         <v>2021</v>
       </c>
       <c r="E74" t="n">
+        <v>4254</v>
+      </c>
+      <c r="F74" t="n">
+        <v>110</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
         <v>4961</v>
       </c>
-      <c r="F74" t="n">
-        <v>145</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>843</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>7</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Soanindrariny Health Centre</t>
         </is>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4604,28 +4801,27 @@
         <v>2448</v>
       </c>
       <c r="E75" t="n">
+        <v>3132</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
         <v>3737</v>
       </c>
-      <c r="F75" t="n">
-        <v>53</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>635</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>5.3</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Soanindrariny Health Centre</t>
         </is>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>5.9</v>
       </c>
     </row>
@@ -4649,28 +4845,31 @@
         <v>2290</v>
       </c>
       <c r="E76" t="n">
+        <v>2973</v>
+      </c>
+      <c r="F76" t="n">
+        <v>30</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
         <v>3543</v>
       </c>
-      <c r="F76" t="n">
-        <v>55</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>602</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>5</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Soanindrariny Health Centre</t>
         </is>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -4694,24 +4893,27 @@
         <v>2430</v>
       </c>
       <c r="E77" t="n">
-        <v>2803</v>
+        <v>2389</v>
       </c>
       <c r="F77" t="n">
-        <v>15</v>
+        <v>-2</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
+        <v>2803</v>
+      </c>
+      <c r="I77" t="n">
         <v>477</v>
       </c>
-      <c r="I77" t="n">
-        <v>4</v>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" t="n">
+        <v>4</v>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Soanindrariny Health Centre</t>
         </is>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4735,24 +4937,27 @@
         <v>2711</v>
       </c>
       <c r="E78" t="n">
-        <v>2738</v>
+        <v>2275</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
+        <v>2738</v>
+      </c>
+      <c r="I78" t="n">
         <v>465</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>3.9</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>7.6</v>
       </c>
     </row>
@@ -4776,28 +4981,31 @@
         <v>1677</v>
       </c>
       <c r="E79" t="n">
+        <v>2299</v>
+      </c>
+      <c r="F79" t="n">
+        <v>37</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
         <v>2665</v>
       </c>
-      <c r="F79" t="n">
-        <v>59</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>453</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>3.8</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Soanindrariny Health Centre</t>
         </is>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -4821,28 +5029,31 @@
         <v>1218</v>
       </c>
       <c r="E80" t="n">
+        <v>2080</v>
+      </c>
+      <c r="F80" t="n">
+        <v>71</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
         <v>2465</v>
       </c>
-      <c r="F80" t="n">
-        <v>102</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>419</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>3.5</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Fanjakamandroso Health Centre</t>
         </is>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -4866,24 +5077,27 @@
         <v>1949</v>
       </c>
       <c r="E81" t="n">
-        <v>2434</v>
+        <v>2112</v>
       </c>
       <c r="F81" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
+        <v>2434</v>
+      </c>
+      <c r="I81" t="n">
         <v>414</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>3.5</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>Soanindrariny Health Centre</t>
         </is>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -4907,24 +5121,27 @@
         <v>2098</v>
       </c>
       <c r="E82" t="n">
-        <v>2064</v>
+        <v>1729</v>
       </c>
       <c r="F82" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
+        <v>2064</v>
+      </c>
+      <c r="I82" t="n">
         <v>351</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>2.9</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4948,24 +5165,27 @@
         <v>1852</v>
       </c>
       <c r="E83" t="n">
-        <v>2066</v>
+        <v>1719</v>
       </c>
       <c r="F83" t="n">
-        <v>12</v>
+        <v>-7</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
+        <v>2066</v>
+      </c>
+      <c r="I83" t="n">
         <v>351</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>2.9</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>3.9</v>
       </c>
     </row>
@@ -4989,24 +5209,31 @@
         <v>2289</v>
       </c>
       <c r="E84" t="n">
+        <v>1364</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
         <v>1653</v>
       </c>
-      <c r="F84" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>281</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>2.3</v>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -5030,24 +5257,27 @@
         <v>1508</v>
       </c>
       <c r="E85" t="n">
-        <v>1284</v>
+        <v>1067</v>
       </c>
       <c r="F85" t="n">
-        <v>-15</v>
+        <v>-29</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
+        <v>1284</v>
+      </c>
+      <c r="I85" t="n">
         <v>218</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>1.8</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5071,24 +5301,27 @@
         <v>1155</v>
       </c>
       <c r="E86" t="n">
-        <v>1160</v>
+        <v>974</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
+        <v>1160</v>
+      </c>
+      <c r="I86" t="n">
         <v>197</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>1.6</v>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -5112,28 +5345,27 @@
         <v>2911</v>
       </c>
       <c r="E87" t="n">
+        <v>3588</v>
+      </c>
+      <c r="F87" t="n">
+        <v>23</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
         <v>4274</v>
       </c>
-      <c r="F87" t="n">
-        <v>47</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>727</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>6.1</v>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5157,24 +5389,27 @@
         <v>3486</v>
       </c>
       <c r="E88" t="n">
-        <v>4134</v>
+        <v>3470</v>
       </c>
       <c r="F88" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
+        <v>4134</v>
+      </c>
+      <c r="I88" t="n">
         <v>703</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>5.9</v>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -5198,24 +5433,27 @@
         <v>2228</v>
       </c>
       <c r="E89" t="n">
-        <v>2879</v>
+        <v>2398</v>
       </c>
       <c r="F89" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
+        <v>2879</v>
+      </c>
+      <c r="I89" t="n">
         <v>489</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>4.1</v>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -5239,24 +5477,27 @@
         <v>2673</v>
       </c>
       <c r="E90" t="n">
-        <v>2853</v>
+        <v>2342</v>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
+        <v>-12</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
+        <v>2853</v>
+      </c>
+      <c r="I90" t="n">
         <v>485</v>
       </c>
-      <c r="I90" t="n">
-        <v>4</v>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -5280,28 +5521,27 @@
         <v>2123</v>
       </c>
       <c r="E91" t="n">
+        <v>2359</v>
+      </c>
+      <c r="F91" t="n">
+        <v>11</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
         <v>2821</v>
       </c>
-      <c r="F91" t="n">
-        <v>33</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>480</v>
       </c>
-      <c r="I91" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" t="n">
+        <v>4</v>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -5325,28 +5565,27 @@
         <v>1802</v>
       </c>
       <c r="E92" t="n">
+        <v>2209</v>
+      </c>
+      <c r="F92" t="n">
+        <v>23</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="n">
         <v>2636</v>
       </c>
-      <c r="F92" t="n">
-        <v>46</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>448</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>3.7</v>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -5370,24 +5609,27 @@
         <v>2124</v>
       </c>
       <c r="E93" t="n">
-        <v>2507</v>
+        <v>2076</v>
       </c>
       <c r="F93" t="n">
-        <v>18</v>
+        <v>-2</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
+        <v>2507</v>
+      </c>
+      <c r="I93" t="n">
         <v>426</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>3.5</v>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5411,24 +5653,27 @@
         <v>2152</v>
       </c>
       <c r="E94" t="n">
-        <v>2431</v>
+        <v>2002</v>
       </c>
       <c r="F94" t="n">
-        <v>13</v>
+        <v>-7</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
+        <v>2431</v>
+      </c>
+      <c r="I94" t="n">
         <v>413</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
         <v>3.4</v>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -5452,28 +5697,27 @@
         <v>1294</v>
       </c>
       <c r="E95" t="n">
+        <v>1594</v>
+      </c>
+      <c r="F95" t="n">
+        <v>23</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
         <v>1899</v>
       </c>
-      <c r="F95" t="n">
-        <v>47</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>323</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>2.7</v>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" t="n">
         <v>6.8</v>
       </c>
     </row>
@@ -5497,24 +5741,27 @@
         <v>1300</v>
       </c>
       <c r="E96" t="n">
-        <v>1615</v>
+        <v>1342</v>
       </c>
       <c r="F96" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
+        <v>1615</v>
+      </c>
+      <c r="I96" t="n">
         <v>275</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>2.3</v>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>Ambatomena Health Centre</t>
         </is>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -5538,28 +5785,27 @@
         <v>1099</v>
       </c>
       <c r="E97" t="n">
+        <v>1208</v>
+      </c>
+      <c r="F97" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
         <v>1464</v>
       </c>
-      <c r="F97" t="n">
-        <v>33</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>249</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
         <v>2.1</v>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -5583,24 +5829,31 @@
         <v>1117</v>
       </c>
       <c r="E98" t="n">
+        <v>747</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
         <v>914</v>
       </c>
-      <c r="F98" t="n">
-        <v>-18</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>155</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
         <v>1.3</v>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Ampanantaovana Health Post</t>
         </is>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -5624,28 +5877,31 @@
         <v>2188</v>
       </c>
       <c r="E99" t="n">
+        <v>4528</v>
+      </c>
+      <c r="F99" t="n">
+        <v>107</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
         <v>5318</v>
       </c>
-      <c r="F99" t="n">
-        <v>143</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>904</v>
       </c>
-      <c r="I99" t="n">
+      <c r="J99" t="n">
         <v>7.5</v>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Vinaninkarena Health Centre</t>
         </is>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -5669,28 +5925,31 @@
         <v>1645</v>
       </c>
       <c r="E100" t="n">
+        <v>3414</v>
+      </c>
+      <c r="F100" t="n">
+        <v>108</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
         <v>3968</v>
       </c>
-      <c r="F100" t="n">
-        <v>141</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>675</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
         <v>5.6</v>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>Vinaninkarena Health Centre</t>
         </is>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" t="n">
         <v>4.1</v>
       </c>
     </row>
@@ -5714,28 +5973,31 @@
         <v>2035</v>
       </c>
       <c r="E101" t="n">
+        <v>3356</v>
+      </c>
+      <c r="F101" t="n">
+        <v>65</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
         <v>3959</v>
       </c>
-      <c r="F101" t="n">
-        <v>95</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>673</v>
       </c>
-      <c r="I101" t="n">
+      <c r="J101" t="n">
         <v>5.6</v>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K101" t="n">
+      <c r="L101" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -5759,28 +6021,31 @@
         <v>1794</v>
       </c>
       <c r="E102" t="n">
+        <v>2826</v>
+      </c>
+      <c r="F102" t="n">
+        <v>58</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
         <v>3355</v>
       </c>
-      <c r="F102" t="n">
-        <v>87</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>570</v>
       </c>
-      <c r="I102" t="n">
+      <c r="J102" t="n">
         <v>4.8</v>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>Vinaninkarena Health Centre</t>
         </is>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -5804,24 +6069,27 @@
         <v>3690</v>
       </c>
       <c r="E103" t="n">
-        <v>3261</v>
+        <v>2611</v>
       </c>
       <c r="F103" t="n">
-        <v>-12</v>
+        <v>-29</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
+        <v>3261</v>
+      </c>
+      <c r="I103" t="n">
         <v>554</v>
       </c>
-      <c r="I103" t="n">
+      <c r="J103" t="n">
         <v>4.6</v>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>Vinaninkarena Health Centre</t>
         </is>
       </c>
-      <c r="K103" t="n">
+      <c r="L103" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -5845,24 +6113,27 @@
         <v>2113</v>
       </c>
       <c r="E104" t="n">
-        <v>2495</v>
+        <v>2036</v>
       </c>
       <c r="F104" t="n">
-        <v>18</v>
+        <v>-4</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
+        <v>2495</v>
+      </c>
+      <c r="I104" t="n">
         <v>424</v>
       </c>
-      <c r="I104" t="n">
+      <c r="J104" t="n">
         <v>3.5</v>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Vinaninkarena Health Centre</t>
         </is>
       </c>
-      <c r="K104" t="n">
+      <c r="L104" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -5886,28 +6157,31 @@
         <v>666</v>
       </c>
       <c r="E105" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F105" t="n">
+        <v>64</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
         <v>1290</v>
       </c>
-      <c r="F105" t="n">
-        <v>94</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>219</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
         <v>1.8</v>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>Vinaninkarena Health Centre</t>
         </is>
       </c>
-      <c r="K105" t="n">
+      <c r="L105" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -5931,28 +6205,31 @@
         <v>1524</v>
       </c>
       <c r="E106" t="n">
+        <v>3322</v>
+      </c>
+      <c r="F106" t="n">
+        <v>118</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
         <v>3831</v>
       </c>
-      <c r="F106" t="n">
-        <v>151</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>651</v>
       </c>
-      <c r="I106" t="n">
+      <c r="J106" t="n">
         <v>5.4</v>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -5976,28 +6253,31 @@
         <v>1719</v>
       </c>
       <c r="E107" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F107" t="n">
+        <v>35</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
         <v>2706</v>
       </c>
-      <c r="F107" t="n">
-        <v>57</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>460</v>
       </c>
-      <c r="I107" t="n">
+      <c r="J107" t="n">
         <v>3.8</v>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K107" t="n">
+      <c r="L107" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -6021,28 +6301,27 @@
         <v>1690</v>
       </c>
       <c r="E108" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F108" t="n">
+        <v>28</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="n">
         <v>2550</v>
       </c>
-      <c r="F108" t="n">
-        <v>51</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>434</v>
       </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
         <v>3.6</v>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K108" t="n">
+      <c r="L108" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -6066,24 +6345,27 @@
         <v>2424</v>
       </c>
       <c r="E109" t="n">
-        <v>2548</v>
+        <v>2147</v>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>-11</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
+        <v>2548</v>
+      </c>
+      <c r="I109" t="n">
         <v>433</v>
       </c>
-      <c r="I109" t="n">
+      <c r="J109" t="n">
         <v>3.6</v>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>Fanjakamandroso Health Centre</t>
         </is>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -6107,24 +6389,27 @@
         <v>1769</v>
       </c>
       <c r="E110" t="n">
-        <v>2133</v>
+        <v>1816</v>
       </c>
       <c r="F110" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
+        <v>2133</v>
+      </c>
+      <c r="I110" t="n">
         <v>363</v>
       </c>
-      <c r="I110" t="n">
-        <v>3</v>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="J110" t="n">
+        <v>3</v>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K110" t="n">
+      <c r="L110" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -6148,28 +6433,27 @@
         <v>1467</v>
       </c>
       <c r="E111" t="n">
+        <v>1837</v>
+      </c>
+      <c r="F111" t="n">
+        <v>25</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="n">
         <v>2135</v>
       </c>
-      <c r="F111" t="n">
-        <v>46</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>363</v>
       </c>
-      <c r="I111" t="n">
-        <v>3</v>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="J111" t="n">
+        <v>3</v>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6193,24 +6477,27 @@
         <v>1959</v>
       </c>
       <c r="E112" t="n">
-        <v>1977</v>
+        <v>1685</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
+        <v>1977</v>
+      </c>
+      <c r="I112" t="n">
         <v>336</v>
       </c>
-      <c r="I112" t="n">
+      <c r="J112" t="n">
         <v>2.8</v>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>Fanjakamandroso Health Centre</t>
         </is>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -6234,28 +6521,27 @@
         <v>1291</v>
       </c>
       <c r="E113" t="n">
+        <v>1493</v>
+      </c>
+      <c r="F113" t="n">
+        <v>16</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="n">
         <v>1716</v>
       </c>
-      <c r="F113" t="n">
-        <v>33</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>292</v>
       </c>
-      <c r="I113" t="n">
+      <c r="J113" t="n">
         <v>2.4</v>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K113" t="n">
+      <c r="L113" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -6279,24 +6565,27 @@
         <v>1419</v>
       </c>
       <c r="E114" t="n">
-        <v>1693</v>
+        <v>1474</v>
       </c>
       <c r="F114" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
+        <v>1693</v>
+      </c>
+      <c r="I114" t="n">
         <v>288</v>
       </c>
-      <c r="I114" t="n">
+      <c r="J114" t="n">
         <v>2.4</v>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K114" t="n">
+      <c r="L114" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -6320,24 +6609,27 @@
         <v>1504</v>
       </c>
       <c r="E115" t="n">
-        <v>1594</v>
+        <v>1346</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>-11</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
+        <v>1594</v>
+      </c>
+      <c r="I115" t="n">
         <v>271</v>
       </c>
-      <c r="I115" t="n">
+      <c r="J115" t="n">
         <v>2.3</v>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -6361,24 +6653,27 @@
         <v>3088</v>
       </c>
       <c r="E116" t="n">
-        <v>3157</v>
+        <v>2612</v>
       </c>
       <c r="F116" t="n">
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
+        <v>3157</v>
+      </c>
+      <c r="I116" t="n">
         <v>537</v>
       </c>
-      <c r="I116" t="n">
+      <c r="J116" t="n">
         <v>4.5</v>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K116" t="n">
+      <c r="L116" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -6402,24 +6697,27 @@
         <v>2842</v>
       </c>
       <c r="E117" t="n">
-        <v>3111</v>
+        <v>2600</v>
       </c>
       <c r="F117" t="n">
-        <v>9</v>
+        <v>-9</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
+        <v>3111</v>
+      </c>
+      <c r="I117" t="n">
         <v>529</v>
       </c>
-      <c r="I117" t="n">
+      <c r="J117" t="n">
         <v>4.4</v>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>Farihitsara Health Post</t>
         </is>
       </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
         <v>6.6</v>
       </c>
     </row>
@@ -6443,24 +6741,27 @@
         <v>2806</v>
       </c>
       <c r="E118" t="n">
-        <v>2509</v>
+        <v>2089</v>
       </c>
       <c r="F118" t="n">
-        <v>-11</v>
+        <v>-26</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
+        <v>2509</v>
+      </c>
+      <c r="I118" t="n">
         <v>427</v>
       </c>
-      <c r="I118" t="n">
+      <c r="J118" t="n">
         <v>3.6</v>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K118" t="n">
+      <c r="L118" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -6484,28 +6785,31 @@
         <v>1223</v>
       </c>
       <c r="E119" t="n">
+        <v>1919</v>
+      </c>
+      <c r="F119" t="n">
+        <v>57</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
         <v>2268</v>
       </c>
-      <c r="F119" t="n">
-        <v>85</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>386</v>
       </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
         <v>3.2</v>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K119" t="n">
+      <c r="L119" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -6529,24 +6833,27 @@
         <v>1812</v>
       </c>
       <c r="E120" t="n">
-        <v>2193</v>
+        <v>1838</v>
       </c>
       <c r="F120" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
+        <v>2193</v>
+      </c>
+      <c r="I120" t="n">
         <v>373</v>
       </c>
-      <c r="I120" t="n">
+      <c r="J120" t="n">
         <v>3.1</v>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K120" t="n">
+      <c r="L120" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -6570,28 +6877,27 @@
         <v>1318</v>
       </c>
       <c r="E121" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F121" t="n">
+        <v>18</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
         <v>1858</v>
       </c>
-      <c r="F121" t="n">
-        <v>41</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>316</v>
       </c>
-      <c r="I121" t="n">
+      <c r="J121" t="n">
         <v>2.6</v>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K121" t="n">
+      <c r="L121" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -6615,28 +6921,31 @@
         <v>1019</v>
       </c>
       <c r="E122" t="n">
+        <v>1532</v>
+      </c>
+      <c r="F122" t="n">
+        <v>50</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
         <v>1801</v>
       </c>
-      <c r="F122" t="n">
-        <v>77</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>306</v>
       </c>
-      <c r="I122" t="n">
+      <c r="J122" t="n">
         <v>2.5</v>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K122" t="n">
+      <c r="L122" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -6660,24 +6969,27 @@
         <v>1907</v>
       </c>
       <c r="E123" t="n">
-        <v>1681</v>
+        <v>1391</v>
       </c>
       <c r="F123" t="n">
-        <v>-12</v>
+        <v>-27</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
+        <v>1681</v>
+      </c>
+      <c r="I123" t="n">
         <v>286</v>
       </c>
-      <c r="I123" t="n">
+      <c r="J123" t="n">
         <v>2.4</v>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>Soamiakatra Health Post</t>
         </is>
       </c>
-      <c r="K123" t="n">
+      <c r="L123" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -6701,24 +7013,31 @@
         <v>1775</v>
       </c>
       <c r="E124" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-39</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
         <v>1286</v>
       </c>
-      <c r="F124" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>219</v>
       </c>
-      <c r="I124" t="n">
+      <c r="J124" t="n">
         <v>1.8</v>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>Farihitsara Health Post</t>
         </is>
       </c>
-      <c r="K124" t="n">
+      <c r="L124" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -6742,28 +7061,31 @@
         <v>2465</v>
       </c>
       <c r="E125" t="n">
+        <v>827</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-66</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
         <v>1027</v>
       </c>
-      <c r="F125" t="n">
-        <v>-58</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>175</v>
       </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
         <v>1.5</v>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K125" t="n">
+      <c r="L125" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -6787,24 +7109,27 @@
         <v>3254</v>
       </c>
       <c r="E126" t="n">
-        <v>3710</v>
+        <v>3177</v>
       </c>
       <c r="F126" t="n">
-        <v>14</v>
+        <v>-2</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
+        <v>3710</v>
+      </c>
+      <c r="I126" t="n">
         <v>631</v>
       </c>
-      <c r="I126" t="n">
+      <c r="J126" t="n">
         <v>5.3</v>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K126" t="n">
+      <c r="L126" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6828,24 +7153,27 @@
         <v>4189</v>
       </c>
       <c r="E127" t="n">
-        <v>3708</v>
+        <v>3216</v>
       </c>
       <c r="F127" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
+        <v>3708</v>
+      </c>
+      <c r="I127" t="n">
         <v>630</v>
       </c>
-      <c r="I127" t="n">
+      <c r="J127" t="n">
         <v>5.2</v>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="K127" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K127" t="n">
+      <c r="L127" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -6869,24 +7197,31 @@
         <v>2804</v>
       </c>
       <c r="E128" t="n">
+        <v>1834</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
         <v>2145</v>
       </c>
-      <c r="F128" t="n">
-        <v>-24</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>365</v>
       </c>
-      <c r="I128" t="n">
-        <v>3</v>
-      </c>
-      <c r="J128" t="inlineStr">
+      <c r="J128" t="n">
+        <v>3</v>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K128" t="n">
+      <c r="L128" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -6910,28 +7245,31 @@
         <v>2865</v>
       </c>
       <c r="E129" t="n">
+        <v>1714</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
         <v>2013</v>
       </c>
-      <c r="F129" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>342</v>
       </c>
-      <c r="I129" t="n">
+      <c r="J129" t="n">
         <v>2.9</v>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K129" t="n">
+      <c r="L129" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6955,24 +7293,31 @@
         <v>2254</v>
       </c>
       <c r="E130" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-31</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
         <v>1808</v>
       </c>
-      <c r="F130" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>307</v>
       </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
         <v>2.6</v>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="K130" t="inlineStr">
         <is>
           <t>Morodrano Health Post</t>
         </is>
       </c>
-      <c r="K130" t="n">
+      <c r="L130" t="n">
         <v>10.1</v>
       </c>
     </row>
@@ -6996,28 +7341,31 @@
         <v>3105</v>
       </c>
       <c r="E131" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-51</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
         <v>1776</v>
       </c>
-      <c r="F131" t="n">
-        <v>-43</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>302</v>
       </c>
-      <c r="I131" t="n">
+      <c r="J131" t="n">
         <v>2.5</v>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="K131" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K131" t="n">
+      <c r="L131" t="n">
         <v>10.3</v>
       </c>
     </row>
@@ -7041,24 +7389,27 @@
         <v>1429</v>
       </c>
       <c r="E132" t="n">
-        <v>1703</v>
+        <v>1466</v>
       </c>
       <c r="F132" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
+        <v>1703</v>
+      </c>
+      <c r="I132" t="n">
         <v>290</v>
       </c>
-      <c r="I132" t="n">
+      <c r="J132" t="n">
         <v>2.4</v>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="K132" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K132" t="n">
+      <c r="L132" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -7082,28 +7433,31 @@
         <v>3073</v>
       </c>
       <c r="E133" t="n">
+        <v>1421</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-54</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
         <v>1670</v>
       </c>
-      <c r="F133" t="n">
-        <v>-46</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>284</v>
       </c>
-      <c r="I133" t="n">
+      <c r="J133" t="n">
         <v>2.4</v>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K133" t="n">
+      <c r="L133" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -7127,28 +7481,31 @@
         <v>1714</v>
       </c>
       <c r="E134" t="n">
+        <v>1028</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
         <v>1205</v>
       </c>
-      <c r="F134" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>205</v>
       </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
         <v>1.7</v>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="K134" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K134" t="n">
+      <c r="L134" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -7172,28 +7529,31 @@
         <v>2200</v>
       </c>
       <c r="E135" t="n">
+        <v>806</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-63</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
         <v>973</v>
       </c>
-      <c r="F135" t="n">
-        <v>-56</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>165</v>
       </c>
-      <c r="I135" t="n">
+      <c r="J135" t="n">
         <v>1.4</v>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>Mandrosohasina Health Centre</t>
         </is>
       </c>
-      <c r="K135" t="n">
+      <c r="L135" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -7217,24 +7577,27 @@
         <v>6041</v>
       </c>
       <c r="E136" t="n">
-        <v>6211</v>
+        <v>5343</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
+        <v>6211</v>
+      </c>
+      <c r="I136" t="n">
         <v>1056</v>
       </c>
-      <c r="I136" t="n">
+      <c r="J136" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="K136" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K136" t="n">
+      <c r="L136" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -7258,24 +7621,27 @@
         <v>2828</v>
       </c>
       <c r="E137" t="n">
-        <v>3116</v>
+        <v>2658</v>
       </c>
       <c r="F137" t="n">
-        <v>10</v>
+        <v>-6</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
+        <v>3116</v>
+      </c>
+      <c r="I137" t="n">
         <v>530</v>
       </c>
-      <c r="I137" t="n">
+      <c r="J137" t="n">
         <v>4.4</v>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -7299,28 +7665,27 @@
         <v>2349</v>
       </c>
       <c r="E138" t="n">
+        <v>2568</v>
+      </c>
+      <c r="F138" t="n">
+        <v>9</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="n">
         <v>3051</v>
       </c>
-      <c r="F138" t="n">
-        <v>30</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>519</v>
       </c>
-      <c r="I138" t="n">
+      <c r="J138" t="n">
         <v>4.3</v>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="K138" t="inlineStr">
         <is>
           <t>Marofangady Health Post</t>
         </is>
       </c>
-      <c r="K138" t="n">
+      <c r="L138" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -7344,24 +7709,31 @@
         <v>3749</v>
       </c>
       <c r="E139" t="n">
+        <v>2245</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
         <v>2682</v>
       </c>
-      <c r="F139" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>456</v>
       </c>
-      <c r="I139" t="n">
+      <c r="J139" t="n">
         <v>3.8</v>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="K139" t="inlineStr">
         <is>
           <t>Marofangady Health Post</t>
         </is>
       </c>
-      <c r="K139" t="n">
+      <c r="L139" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -7385,28 +7757,31 @@
         <v>4656</v>
       </c>
       <c r="E140" t="n">
+        <v>2114</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
         <v>2527</v>
       </c>
-      <c r="F140" t="n">
-        <v>-46</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>430</v>
       </c>
-      <c r="I140" t="n">
+      <c r="J140" t="n">
         <v>3.6</v>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="K140" t="inlineStr">
         <is>
           <t>Marofangady Health Post</t>
         </is>
       </c>
-      <c r="K140" t="n">
+      <c r="L140" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -7430,24 +7805,27 @@
         <v>1241</v>
       </c>
       <c r="E141" t="n">
-        <v>1555</v>
+        <v>1334</v>
       </c>
       <c r="F141" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
+        <v>1555</v>
+      </c>
+      <c r="I141" t="n">
         <v>264</v>
       </c>
-      <c r="I141" t="n">
+      <c r="J141" t="n">
         <v>2.2</v>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="K141" t="inlineStr">
         <is>
           <t>Marofangady Health Post</t>
         </is>
       </c>
-      <c r="K141" t="n">
+      <c r="L141" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -7471,28 +7849,31 @@
         <v>2170</v>
       </c>
       <c r="E142" t="n">
+        <v>1213</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
         <v>1428</v>
       </c>
-      <c r="F142" t="n">
-        <v>-34</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>243</v>
       </c>
-      <c r="I142" t="n">
+      <c r="J142" t="n">
         <v>2</v>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="K142" t="inlineStr">
         <is>
           <t>Ambano Health Centre</t>
         </is>
       </c>
-      <c r="K142" t="n">
+      <c r="L142" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -7516,24 +7897,27 @@
         <v>5602</v>
       </c>
       <c r="E143" t="n">
-        <v>6810</v>
+        <v>5790</v>
       </c>
       <c r="F143" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
+        <v>6810</v>
+      </c>
+      <c r="I143" t="n">
         <v>1158</v>
       </c>
-      <c r="I143" t="n">
+      <c r="J143" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="K143" t="inlineStr">
         <is>
           <t>Antsoantany Health Centre</t>
         </is>
       </c>
-      <c r="K143" t="n">
+      <c r="L143" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -7557,28 +7941,31 @@
         <v>2125</v>
       </c>
       <c r="E144" t="n">
+        <v>4294</v>
+      </c>
+      <c r="F144" t="n">
+        <v>102</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
         <v>5117</v>
       </c>
-      <c r="F144" t="n">
-        <v>141</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
+      <c r="I144" t="n">
         <v>870</v>
       </c>
-      <c r="I144" t="n">
+      <c r="J144" t="n">
         <v>7.2</v>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="K144" t="inlineStr">
         <is>
           <t>Antsoantany Health Centre</t>
         </is>
       </c>
-      <c r="K144" t="n">
+      <c r="L144" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -7602,24 +7989,27 @@
         <v>2377</v>
       </c>
       <c r="E145" t="n">
-        <v>2363</v>
+        <v>1971</v>
       </c>
       <c r="F145" t="n">
-        <v>-1</v>
+        <v>-17</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
+        <v>2363</v>
+      </c>
+      <c r="I145" t="n">
         <v>402</v>
       </c>
-      <c r="I145" t="n">
+      <c r="J145" t="n">
         <v>3.4</v>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="K145" t="inlineStr">
         <is>
           <t>Amberobe Health Centre</t>
         </is>
       </c>
-      <c r="K145" t="n">
+      <c r="L145" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -7643,28 +8033,31 @@
         <v>1381</v>
       </c>
       <c r="E146" t="n">
+        <v>1921</v>
+      </c>
+      <c r="F146" t="n">
+        <v>39</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
         <v>2292</v>
       </c>
-      <c r="F146" t="n">
-        <v>66</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
+      <c r="I146" t="n">
         <v>390</v>
       </c>
-      <c r="I146" t="n">
+      <c r="J146" t="n">
         <v>3.2</v>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="K146" t="inlineStr">
         <is>
           <t>Ambohibary Health Centre</t>
         </is>
       </c>
-      <c r="K146" t="n">
+      <c r="L146" t="n">
         <v>4.7</v>
       </c>
     </row>
@@ -7688,28 +8081,31 @@
         <v>1137</v>
       </c>
       <c r="E147" t="n">
+        <v>1496</v>
+      </c>
+      <c r="F147" t="n">
+        <v>32</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
         <v>1790</v>
       </c>
-      <c r="F147" t="n">
-        <v>57</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
+      <c r="I147" t="n">
         <v>304</v>
       </c>
-      <c r="I147" t="n">
+      <c r="J147" t="n">
         <v>2.5</v>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="K147" t="inlineStr">
         <is>
           <t>Antsoantany Health Centre</t>
         </is>
       </c>
-      <c r="K147" t="n">
+      <c r="L147" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -7733,28 +8129,31 @@
         <v>1284</v>
       </c>
       <c r="E148" t="n">
+        <v>1812</v>
+      </c>
+      <c r="F148" t="n">
+        <v>41</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
         <v>2112</v>
       </c>
-      <c r="F148" t="n">
-        <v>64</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
+      <c r="I148" t="n">
         <v>359</v>
       </c>
-      <c r="I148" t="n">
-        <v>3</v>
-      </c>
-      <c r="J148" t="inlineStr">
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K148" t="n">
+      <c r="L148" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7778,28 +8177,31 @@
         <v>2979</v>
       </c>
       <c r="E149" t="n">
+        <v>1772</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-41</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
         <v>2066</v>
       </c>
-      <c r="F149" t="n">
-        <v>-31</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
+      <c r="I149" t="n">
         <v>351</v>
       </c>
-      <c r="I149" t="n">
+      <c r="J149" t="n">
         <v>2.9</v>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="K149" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K149" t="n">
+      <c r="L149" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -7823,24 +8225,27 @@
         <v>2057</v>
       </c>
       <c r="E150" t="n">
-        <v>1864</v>
+        <v>1545</v>
       </c>
       <c r="F150" t="n">
-        <v>-9</v>
+        <v>-25</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
+        <v>1864</v>
+      </c>
+      <c r="I150" t="n">
         <v>317</v>
       </c>
-      <c r="I150" t="n">
+      <c r="J150" t="n">
         <v>2.6</v>
       </c>
-      <c r="J150" t="inlineStr">
+      <c r="K150" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K150" t="n">
+      <c r="L150" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -7864,28 +8269,31 @@
         <v>921</v>
       </c>
       <c r="E151" t="n">
+        <v>1531</v>
+      </c>
+      <c r="F151" t="n">
+        <v>66</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
         <v>1848</v>
       </c>
-      <c r="F151" t="n">
-        <v>101</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
+      <c r="I151" t="n">
         <v>314</v>
       </c>
-      <c r="I151" t="n">
+      <c r="J151" t="n">
         <v>2.6</v>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="K151" t="inlineStr">
         <is>
           <t>Farihitsara Health Post</t>
         </is>
       </c>
-      <c r="K151" t="n">
+      <c r="L151" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -7909,24 +8317,31 @@
         <v>2254</v>
       </c>
       <c r="E152" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
         <v>1634</v>
       </c>
-      <c r="F152" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="n">
+      <c r="I152" t="n">
         <v>278</v>
       </c>
-      <c r="I152" t="n">
+      <c r="J152" t="n">
         <v>2.3</v>
       </c>
-      <c r="J152" t="inlineStr">
+      <c r="K152" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K152" t="n">
+      <c r="L152" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -7950,28 +8365,31 @@
         <v>916</v>
       </c>
       <c r="E153" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F153" t="n">
+        <v>48</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
         <v>1600</v>
       </c>
-      <c r="F153" t="n">
-        <v>75</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H153" t="n">
+      <c r="I153" t="n">
         <v>272</v>
       </c>
-      <c r="I153" t="n">
+      <c r="J153" t="n">
         <v>2.3</v>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="K153" t="inlineStr">
         <is>
           <t>Farihitsara Health Post</t>
         </is>
       </c>
-      <c r="K153" t="n">
+      <c r="L153" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -7995,24 +8413,27 @@
         <v>1691</v>
       </c>
       <c r="E154" t="n">
-        <v>1508</v>
+        <v>1250</v>
       </c>
       <c r="F154" t="n">
-        <v>-11</v>
+        <v>-26</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="n">
+        <v>1508</v>
+      </c>
+      <c r="I154" t="n">
         <v>256</v>
       </c>
-      <c r="I154" t="n">
+      <c r="J154" t="n">
         <v>2.1</v>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="K154" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K154" t="n">
+      <c r="L154" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -8036,28 +8457,31 @@
         <v>795</v>
       </c>
       <c r="E155" t="n">
+        <v>1171</v>
+      </c>
+      <c r="F155" t="n">
+        <v>47</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
         <v>1382</v>
       </c>
-      <c r="F155" t="n">
-        <v>74</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H155" t="n">
+      <c r="I155" t="n">
         <v>235</v>
       </c>
-      <c r="I155" t="n">
+      <c r="J155" t="n">
         <v>2</v>
       </c>
-      <c r="J155" t="inlineStr">
+      <c r="K155" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K155" t="n">
+      <c r="L155" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -8081,24 +8505,27 @@
         <v>1167</v>
       </c>
       <c r="E156" t="n">
-        <v>1375</v>
+        <v>1172</v>
       </c>
       <c r="F156" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
+        <v>1375</v>
+      </c>
+      <c r="I156" t="n">
         <v>234</v>
       </c>
-      <c r="I156" t="n">
+      <c r="J156" t="n">
         <v>1.9</v>
       </c>
-      <c r="J156" t="inlineStr">
+      <c r="K156" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K156" t="n">
+      <c r="L156" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -8122,24 +8549,31 @@
         <v>1744</v>
       </c>
       <c r="E157" t="n">
+        <v>1144</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
         <v>1357</v>
       </c>
-      <c r="F157" t="n">
-        <v>-22</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="n">
+      <c r="I157" t="n">
         <v>231</v>
       </c>
-      <c r="I157" t="n">
+      <c r="J157" t="n">
         <v>1.9</v>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="K157" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K157" t="n">
+      <c r="L157" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -8163,24 +8597,27 @@
         <v>1142</v>
       </c>
       <c r="E158" t="n">
-        <v>961</v>
+        <v>813</v>
       </c>
       <c r="F158" t="n">
-        <v>-16</v>
+        <v>-29</v>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
+        <v>961</v>
+      </c>
+      <c r="I158" t="n">
         <v>163</v>
       </c>
-      <c r="I158" t="n">
+      <c r="J158" t="n">
         <v>1.4</v>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="K158" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K158" t="n">
+      <c r="L158" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -8204,28 +8641,27 @@
         <v>2181</v>
       </c>
       <c r="E159" t="n">
+        <v>2724</v>
+      </c>
+      <c r="F159" t="n">
+        <v>25</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="n">
         <v>3134</v>
       </c>
-      <c r="F159" t="n">
-        <v>44</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H159" t="n">
+      <c r="I159" t="n">
         <v>533</v>
       </c>
-      <c r="I159" t="n">
+      <c r="J159" t="n">
         <v>4.4</v>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="K159" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K159" t="n">
+      <c r="L159" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -8249,28 +8685,27 @@
         <v>2264</v>
       </c>
       <c r="E160" t="n">
+        <v>2631</v>
+      </c>
+      <c r="F160" t="n">
+        <v>16</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="n">
         <v>3047</v>
       </c>
-      <c r="F160" t="n">
-        <v>35</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H160" t="n">
+      <c r="I160" t="n">
         <v>518</v>
       </c>
-      <c r="I160" t="n">
+      <c r="J160" t="n">
         <v>4.3</v>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="K160" t="inlineStr">
         <is>
           <t>Belazao Health Centre</t>
         </is>
       </c>
-      <c r="K160" t="n">
+      <c r="L160" t="n">
         <v>4.1</v>
       </c>
     </row>
@@ -8294,28 +8729,31 @@
         <v>1602</v>
       </c>
       <c r="E161" t="n">
+        <v>2492</v>
+      </c>
+      <c r="F161" t="n">
+        <v>56</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
         <v>2917</v>
       </c>
-      <c r="F161" t="n">
-        <v>82</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H161" t="n">
+      <c r="I161" t="n">
         <v>496</v>
       </c>
-      <c r="I161" t="n">
+      <c r="J161" t="n">
         <v>4.1</v>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="K161" t="inlineStr">
         <is>
           <t>Belazao Health Centre</t>
         </is>
       </c>
-      <c r="K161" t="n">
+      <c r="L161" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -8339,24 +8777,27 @@
         <v>2843</v>
       </c>
       <c r="E162" t="n">
-        <v>2433</v>
+        <v>2078</v>
       </c>
       <c r="F162" t="n">
-        <v>-14</v>
+        <v>-27</v>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="n">
+        <v>2433</v>
+      </c>
+      <c r="I162" t="n">
         <v>414</v>
       </c>
-      <c r="I162" t="n">
+      <c r="J162" t="n">
         <v>3.5</v>
       </c>
-      <c r="J162" t="inlineStr">
+      <c r="K162" t="inlineStr">
         <is>
           <t>Belazao Health Centre</t>
         </is>
       </c>
-      <c r="K162" t="n">
+      <c r="L162" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -8380,24 +8821,27 @@
         <v>2355</v>
       </c>
       <c r="E163" t="n">
-        <v>2256</v>
+        <v>1974</v>
       </c>
       <c r="F163" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
+        <v>2256</v>
+      </c>
+      <c r="I163" t="n">
         <v>384</v>
       </c>
-      <c r="I163" t="n">
+      <c r="J163" t="n">
         <v>3.2</v>
       </c>
-      <c r="J163" t="inlineStr">
+      <c r="K163" t="inlineStr">
         <is>
           <t>Belazao Health Centre</t>
         </is>
       </c>
-      <c r="K163" t="n">
+      <c r="L163" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -8421,24 +8865,27 @@
         <v>2004</v>
       </c>
       <c r="E164" t="n">
-        <v>1931</v>
+        <v>1666</v>
       </c>
       <c r="F164" t="n">
-        <v>-4</v>
+        <v>-17</v>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
+        <v>1931</v>
+      </c>
+      <c r="I164" t="n">
         <v>328</v>
       </c>
-      <c r="I164" t="n">
+      <c r="J164" t="n">
         <v>2.7</v>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="K164" t="inlineStr">
         <is>
           <t>Belazao Health Centre</t>
         </is>
       </c>
-      <c r="K164" t="n">
+      <c r="L164" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -8462,24 +8909,27 @@
         <v>1083</v>
       </c>
       <c r="E165" t="n">
-        <v>1040</v>
+        <v>908</v>
       </c>
       <c r="F165" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="n">
+        <v>1040</v>
+      </c>
+      <c r="I165" t="n">
         <v>177</v>
       </c>
-      <c r="I165" t="n">
+      <c r="J165" t="n">
         <v>1.5</v>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="K165" t="inlineStr">
         <is>
           <t>Belazao Health Centre</t>
         </is>
       </c>
-      <c r="K165" t="n">
+      <c r="L165" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -8503,28 +8953,31 @@
         <v>3071</v>
       </c>
       <c r="E166" t="n">
+        <v>4594</v>
+      </c>
+      <c r="F166" t="n">
+        <v>50</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
         <v>5495</v>
       </c>
-      <c r="F166" t="n">
-        <v>79</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H166" t="n">
+      <c r="I166" t="n">
         <v>934</v>
       </c>
-      <c r="I166" t="n">
+      <c r="J166" t="n">
         <v>7.8</v>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="K166" t="inlineStr">
         <is>
           <t>Laimbolo Health Post</t>
         </is>
       </c>
-      <c r="K166" t="n">
+      <c r="L166" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -8548,28 +9001,27 @@
         <v>1954</v>
       </c>
       <c r="E167" t="n">
+        <v>2270</v>
+      </c>
+      <c r="F167" t="n">
+        <v>16</v>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="n">
         <v>2718</v>
       </c>
-      <c r="F167" t="n">
-        <v>39</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H167" t="n">
+      <c r="I167" t="n">
         <v>462</v>
       </c>
-      <c r="I167" t="n">
+      <c r="J167" t="n">
         <v>3.9</v>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K167" t="n">
+      <c r="L167" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -8593,24 +9045,27 @@
         <v>1919</v>
       </c>
       <c r="E168" t="n">
-        <v>2344</v>
+        <v>1970</v>
       </c>
       <c r="F168" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
+        <v>2344</v>
+      </c>
+      <c r="I168" t="n">
         <v>398</v>
       </c>
-      <c r="I168" t="n">
+      <c r="J168" t="n">
         <v>3.3</v>
       </c>
-      <c r="J168" t="inlineStr">
+      <c r="K168" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K168" t="n">
+      <c r="L168" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -8634,28 +9089,27 @@
         <v>1737</v>
       </c>
       <c r="E169" t="n">
+        <v>1888</v>
+      </c>
+      <c r="F169" t="n">
+        <v>9</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="n">
         <v>2258</v>
       </c>
-      <c r="F169" t="n">
-        <v>30</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H169" t="n">
+      <c r="I169" t="n">
         <v>384</v>
       </c>
-      <c r="I169" t="n">
+      <c r="J169" t="n">
         <v>3.2</v>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>Farihitsara Health Post</t>
         </is>
       </c>
-      <c r="K169" t="n">
+      <c r="L169" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -8679,28 +9133,31 @@
         <v>872</v>
       </c>
       <c r="E170" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F170" t="n">
+        <v>42</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
         <v>1478</v>
       </c>
-      <c r="F170" t="n">
-        <v>69</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H170" t="n">
+      <c r="I170" t="n">
         <v>251</v>
       </c>
-      <c r="I170" t="n">
+      <c r="J170" t="n">
         <v>2.1</v>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="K170" t="inlineStr">
         <is>
           <t>Laimbolo Health Post</t>
         </is>
       </c>
-      <c r="K170" t="n">
+      <c r="L170" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -8724,24 +9181,27 @@
         <v>1201</v>
       </c>
       <c r="E171" t="n">
-        <v>1351</v>
+        <v>1147</v>
       </c>
       <c r="F171" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
+        <v>1351</v>
+      </c>
+      <c r="I171" t="n">
         <v>230</v>
       </c>
-      <c r="I171" t="n">
+      <c r="J171" t="n">
         <v>1.9</v>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="K171" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K171" t="n">
+      <c r="L171" t="n">
         <v>7.9</v>
       </c>
     </row>
@@ -8765,24 +9225,27 @@
         <v>694</v>
       </c>
       <c r="E172" t="n">
-        <v>796</v>
+        <v>681</v>
       </c>
       <c r="F172" t="n">
-        <v>15</v>
+        <v>-2</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="n">
+        <v>796</v>
+      </c>
+      <c r="I172" t="n">
         <v>135</v>
       </c>
-      <c r="I172" t="n">
+      <c r="J172" t="n">
         <v>1.1</v>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="K172" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K172" t="n">
+      <c r="L172" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -8806,28 +9269,31 @@
         <v>2311</v>
       </c>
       <c r="E173" t="n">
+        <v>3018</v>
+      </c>
+      <c r="F173" t="n">
+        <v>31</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
         <v>3593</v>
       </c>
-      <c r="F173" t="n">
-        <v>55</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H173" t="n">
+      <c r="I173" t="n">
         <v>611</v>
       </c>
-      <c r="I173" t="n">
+      <c r="J173" t="n">
         <v>5.1</v>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>Ambohimiarivo Health Centre</t>
         </is>
       </c>
-      <c r="K173" t="n">
+      <c r="L173" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -8851,28 +9317,31 @@
         <v>1294</v>
       </c>
       <c r="E174" t="n">
+        <v>2125</v>
+      </c>
+      <c r="F174" t="n">
+        <v>64</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
         <v>2476</v>
       </c>
-      <c r="F174" t="n">
-        <v>91</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H174" t="n">
+      <c r="I174" t="n">
         <v>421</v>
       </c>
-      <c r="I174" t="n">
+      <c r="J174" t="n">
         <v>3.5</v>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K174" t="n">
+      <c r="L174" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -8896,24 +9365,27 @@
         <v>2792</v>
       </c>
       <c r="E175" t="n">
-        <v>2400</v>
+        <v>2023</v>
       </c>
       <c r="F175" t="n">
-        <v>-14</v>
+        <v>-28</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I175" t="n">
         <v>408</v>
       </c>
-      <c r="I175" t="n">
+      <c r="J175" t="n">
         <v>3.4</v>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="K175" t="inlineStr">
         <is>
           <t>Ambohimiarivo Health Centre</t>
         </is>
       </c>
-      <c r="K175" t="n">
+      <c r="L175" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -8937,28 +9409,27 @@
         <v>1674</v>
       </c>
       <c r="E176" t="n">
+        <v>1828</v>
+      </c>
+      <c r="F176" t="n">
+        <v>9</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="n">
         <v>2186</v>
       </c>
-      <c r="F176" t="n">
-        <v>31</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H176" t="n">
+      <c r="I176" t="n">
         <v>372</v>
       </c>
-      <c r="I176" t="n">
+      <c r="J176" t="n">
         <v>3.1</v>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="K176" t="inlineStr">
         <is>
           <t>Amberobe Health Centre</t>
         </is>
       </c>
-      <c r="K176" t="n">
+      <c r="L176" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -8982,28 +9453,31 @@
         <v>1043</v>
       </c>
       <c r="E177" t="n">
+        <v>1635</v>
+      </c>
+      <c r="F177" t="n">
+        <v>57</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
         <v>1932</v>
       </c>
-      <c r="F177" t="n">
-        <v>85</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H177" t="n">
+      <c r="I177" t="n">
         <v>328</v>
       </c>
-      <c r="I177" t="n">
+      <c r="J177" t="n">
         <v>2.7</v>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="K177" t="inlineStr">
         <is>
           <t>Ambohidranandriana Health Centre</t>
         </is>
       </c>
-      <c r="K177" t="n">
+      <c r="L177" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -9027,28 +9501,27 @@
         <v>1409</v>
       </c>
       <c r="E178" t="n">
+        <v>1549</v>
+      </c>
+      <c r="F178" t="n">
+        <v>10</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="n">
         <v>1856</v>
       </c>
-      <c r="F178" t="n">
-        <v>32</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H178" t="n">
+      <c r="I178" t="n">
         <v>316</v>
       </c>
-      <c r="I178" t="n">
+      <c r="J178" t="n">
         <v>2.6</v>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="K178" t="inlineStr">
         <is>
           <t>Ambohimiarivo Health Centre</t>
         </is>
       </c>
-      <c r="K178" t="n">
+      <c r="L178" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -9072,28 +9545,31 @@
         <v>864</v>
       </c>
       <c r="E179" t="n">
+        <v>1314</v>
+      </c>
+      <c r="F179" t="n">
+        <v>52</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
         <v>1550</v>
       </c>
-      <c r="F179" t="n">
-        <v>79</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H179" t="n">
+      <c r="I179" t="n">
         <v>264</v>
       </c>
-      <c r="I179" t="n">
+      <c r="J179" t="n">
         <v>2.2</v>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t>Ambohimiarivo Health Centre</t>
         </is>
       </c>
-      <c r="K179" t="n">
+      <c r="L179" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -9117,28 +9593,31 @@
         <v>1430</v>
       </c>
       <c r="E180" t="n">
+        <v>2623</v>
+      </c>
+      <c r="F180" t="n">
+        <v>83</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
         <v>3043</v>
       </c>
-      <c r="F180" t="n">
-        <v>113</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H180" t="n">
+      <c r="I180" t="n">
         <v>517</v>
       </c>
-      <c r="I180" t="n">
+      <c r="J180" t="n">
         <v>4.3</v>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>Vinaninkarena Health Centre</t>
         </is>
       </c>
-      <c r="K180" t="n">
+      <c r="L180" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9162,28 +9641,31 @@
         <v>1444</v>
       </c>
       <c r="E181" t="n">
+        <v>2354</v>
+      </c>
+      <c r="F181" t="n">
+        <v>63</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
         <v>2733</v>
       </c>
-      <c r="F181" t="n">
-        <v>89</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H181" t="n">
+      <c r="I181" t="n">
         <v>465</v>
       </c>
-      <c r="I181" t="n">
+      <c r="J181" t="n">
         <v>3.9</v>
       </c>
-      <c r="J181" t="inlineStr">
+      <c r="K181" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K181" t="n">
+      <c r="L181" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -9207,28 +9689,27 @@
         <v>1427</v>
       </c>
       <c r="E182" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F182" t="n">
+        <v>23</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="n">
         <v>2022</v>
       </c>
-      <c r="F182" t="n">
-        <v>42</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H182" t="n">
+      <c r="I182" t="n">
         <v>344</v>
       </c>
-      <c r="I182" t="n">
+      <c r="J182" t="n">
         <v>2.9</v>
       </c>
-      <c r="J182" t="inlineStr">
+      <c r="K182" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K182" t="n">
+      <c r="L182" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -9252,28 +9733,31 @@
         <v>685</v>
       </c>
       <c r="E183" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F183" t="n">
+        <v>99</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
         <v>1603</v>
       </c>
-      <c r="F183" t="n">
-        <v>134</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H183" t="n">
+      <c r="I183" t="n">
         <v>273</v>
       </c>
-      <c r="I183" t="n">
+      <c r="J183" t="n">
         <v>2.3</v>
       </c>
-      <c r="J183" t="inlineStr">
+      <c r="K183" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K183" t="n">
+      <c r="L183" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -9297,24 +9781,27 @@
         <v>1255</v>
       </c>
       <c r="E184" t="n">
-        <v>1467</v>
+        <v>1253</v>
       </c>
       <c r="F184" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
+        <v>1467</v>
+      </c>
+      <c r="I184" t="n">
         <v>249</v>
       </c>
-      <c r="I184" t="n">
+      <c r="J184" t="n">
         <v>2.1</v>
       </c>
-      <c r="J184" t="inlineStr">
+      <c r="K184" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K184" t="n">
+      <c r="L184" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -9338,24 +9825,27 @@
         <v>1274</v>
       </c>
       <c r="E185" t="n">
-        <v>1234</v>
+        <v>1053</v>
       </c>
       <c r="F185" t="n">
-        <v>-3</v>
+        <v>-17</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
+        <v>1234</v>
+      </c>
+      <c r="I185" t="n">
         <v>210</v>
       </c>
-      <c r="I185" t="n">
+      <c r="J185" t="n">
         <v>1.8</v>
       </c>
-      <c r="J185" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K185" t="n">
+      <c r="L185" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -9379,24 +9869,31 @@
         <v>1509</v>
       </c>
       <c r="E186" t="n">
+        <v>959</v>
+      </c>
+      <c r="F186" t="n">
+        <v>-36</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
         <v>1143</v>
       </c>
-      <c r="F186" t="n">
-        <v>-24</v>
-      </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="n">
+      <c r="I186" t="n">
         <v>194</v>
       </c>
-      <c r="I186" t="n">
+      <c r="J186" t="n">
         <v>1.6</v>
       </c>
-      <c r="J186" t="inlineStr">
+      <c r="K186" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K186" t="n">
+      <c r="L186" t="n">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -9420,24 +9917,27 @@
         <v>897</v>
       </c>
       <c r="E187" t="n">
-        <v>985</v>
+        <v>829</v>
       </c>
       <c r="F187" t="n">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="n">
+        <v>985</v>
+      </c>
+      <c r="I187" t="n">
         <v>167</v>
       </c>
-      <c r="I187" t="n">
+      <c r="J187" t="n">
         <v>1.4</v>
       </c>
-      <c r="J187" t="inlineStr">
+      <c r="K187" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K187" t="n">
+      <c r="L187" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -9461,28 +9961,27 @@
         <v>641</v>
       </c>
       <c r="E188" t="n">
+        <v>742</v>
+      </c>
+      <c r="F188" t="n">
+        <v>16</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="n">
         <v>864</v>
       </c>
-      <c r="F188" t="n">
-        <v>35</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H188" t="n">
+      <c r="I188" t="n">
         <v>147</v>
       </c>
-      <c r="I188" t="n">
+      <c r="J188" t="n">
         <v>1.2</v>
       </c>
-      <c r="J188" t="inlineStr">
+      <c r="K188" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K188" t="n">
+      <c r="L188" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -9506,28 +10005,31 @@
         <v>865</v>
       </c>
       <c r="E189" t="n">
+        <v>451</v>
+      </c>
+      <c r="F189" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
         <v>537</v>
       </c>
-      <c r="F189" t="n">
-        <v>-38</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H189" t="n">
+      <c r="I189" t="n">
         <v>91</v>
       </c>
-      <c r="I189" t="n">
+      <c r="J189" t="n">
         <v>0.8</v>
       </c>
-      <c r="J189" t="inlineStr">
+      <c r="K189" t="inlineStr">
         <is>
           <t>Mangarano Health Centre</t>
         </is>
       </c>
-      <c r="K189" t="n">
+      <c r="L189" t="n">
         <v>6.3</v>
       </c>
     </row>
@@ -9551,28 +10053,31 @@
         <v>2080</v>
       </c>
       <c r="E190" t="n">
+        <v>3217</v>
+      </c>
+      <c r="F190" t="n">
+        <v>55</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
         <v>3755</v>
       </c>
-      <c r="F190" t="n">
-        <v>81</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H190" t="n">
+      <c r="I190" t="n">
         <v>638</v>
       </c>
-      <c r="I190" t="n">
+      <c r="J190" t="n">
         <v>5.3</v>
       </c>
-      <c r="J190" t="inlineStr">
+      <c r="K190" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K190" t="n">
+      <c r="L190" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -9596,28 +10101,31 @@
         <v>1510</v>
       </c>
       <c r="E191" t="n">
+        <v>2506</v>
+      </c>
+      <c r="F191" t="n">
+        <v>66</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
         <v>2981</v>
       </c>
-      <c r="F191" t="n">
-        <v>97</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H191" t="n">
+      <c r="I191" t="n">
         <v>507</v>
       </c>
-      <c r="I191" t="n">
+      <c r="J191" t="n">
         <v>4.2</v>
       </c>
-      <c r="J191" t="inlineStr">
+      <c r="K191" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K191" t="n">
+      <c r="L191" t="n">
         <v>7.6</v>
       </c>
     </row>
@@ -9641,24 +10149,27 @@
         <v>2354</v>
       </c>
       <c r="E192" t="n">
-        <v>2490</v>
+        <v>2118</v>
       </c>
       <c r="F192" t="n">
-        <v>6</v>
+        <v>-10</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
+        <v>2490</v>
+      </c>
+      <c r="I192" t="n">
         <v>423</v>
       </c>
-      <c r="I192" t="n">
+      <c r="J192" t="n">
         <v>3.5</v>
       </c>
-      <c r="J192" t="inlineStr">
+      <c r="K192" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K192" t="n">
+      <c r="L192" t="n">
         <v>9</v>
       </c>
     </row>
@@ -9682,28 +10193,31 @@
         <v>1434</v>
       </c>
       <c r="E193" t="n">
+        <v>1874</v>
+      </c>
+      <c r="F193" t="n">
+        <v>31</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
         <v>2234</v>
       </c>
-      <c r="F193" t="n">
-        <v>56</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H193" t="n">
+      <c r="I193" t="n">
         <v>380</v>
       </c>
-      <c r="I193" t="n">
+      <c r="J193" t="n">
         <v>3.2</v>
       </c>
-      <c r="J193" t="inlineStr">
+      <c r="K193" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K193" t="n">
+      <c r="L193" t="n">
         <v>11.3</v>
       </c>
     </row>
@@ -9727,24 +10241,31 @@
         <v>1714</v>
       </c>
       <c r="E194" t="n">
+        <v>1201</v>
+      </c>
+      <c r="F194" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
         <v>1449</v>
       </c>
-      <c r="F194" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="n">
+      <c r="I194" t="n">
         <v>246</v>
       </c>
-      <c r="I194" t="n">
+      <c r="J194" t="n">
         <v>2</v>
       </c>
-      <c r="J194" t="inlineStr">
+      <c r="K194" t="inlineStr">
         <is>
           <t>Manandona Health Centre</t>
         </is>
       </c>
-      <c r="K194" t="n">
+      <c r="L194" t="n">
         <v>10.3</v>
       </c>
     </row>
@@ -9768,24 +10289,27 @@
         <v>1524</v>
       </c>
       <c r="E195" t="n">
-        <v>1366</v>
+        <v>1171</v>
       </c>
       <c r="F195" t="n">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="n">
+        <v>1366</v>
+      </c>
+      <c r="I195" t="n">
         <v>232</v>
       </c>
-      <c r="I195" t="n">
+      <c r="J195" t="n">
         <v>1.9</v>
       </c>
-      <c r="J195" t="inlineStr">
+      <c r="K195" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K195" t="n">
+      <c r="L195" t="n">
         <v>11.9</v>
       </c>
     </row>
@@ -9809,24 +10333,31 @@
         <v>924</v>
       </c>
       <c r="E196" t="n">
+        <v>595</v>
+      </c>
+      <c r="F196" t="n">
+        <v>-36</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
         <v>709</v>
       </c>
-      <c r="F196" t="n">
-        <v>-23</v>
-      </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="n">
+      <c r="I196" t="n">
         <v>121</v>
       </c>
-      <c r="I196" t="n">
+      <c r="J196" t="n">
         <v>1</v>
       </c>
-      <c r="J196" t="inlineStr">
+      <c r="K196" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K196" t="n">
+      <c r="L196" t="n">
         <v>14</v>
       </c>
     </row>
@@ -9850,28 +10381,31 @@
         <v>1227</v>
       </c>
       <c r="E197" t="n">
+        <v>406</v>
+      </c>
+      <c r="F197" t="n">
+        <v>-67</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
         <v>477</v>
       </c>
-      <c r="F197" t="n">
-        <v>-61</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H197" t="n">
+      <c r="I197" t="n">
         <v>81</v>
       </c>
-      <c r="I197" t="n">
+      <c r="J197" t="n">
         <v>0.7</v>
       </c>
-      <c r="J197" t="inlineStr">
+      <c r="K197" t="inlineStr">
         <is>
           <t>Sahanivotry Atsimo Health Centre</t>
         </is>
       </c>
-      <c r="K197" t="n">
+      <c r="L197" t="n">
         <v>15.3</v>
       </c>
     </row>
@@ -9895,24 +10429,31 @@
         <v>2681</v>
       </c>
       <c r="E198" t="n">
+        <v>1642</v>
+      </c>
+      <c r="F198" t="n">
+        <v>-39</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
         <v>1893</v>
       </c>
-      <c r="F198" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="n">
+      <c r="I198" t="n">
         <v>322</v>
       </c>
-      <c r="I198" t="n">
+      <c r="J198" t="n">
         <v>2.7</v>
       </c>
-      <c r="J198" t="inlineStr">
+      <c r="K198" t="inlineStr">
         <is>
           <t>Belazao Health Centre</t>
         </is>
       </c>
-      <c r="K198" t="n">
+      <c r="L198" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -9936,24 +10477,27 @@
         <v>1350</v>
       </c>
       <c r="E199" t="n">
-        <v>1747</v>
+        <v>1501</v>
       </c>
       <c r="F199" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="n">
+        <v>1747</v>
+      </c>
+      <c r="I199" t="n">
         <v>297</v>
       </c>
-      <c r="I199" t="n">
+      <c r="J199" t="n">
         <v>2.5</v>
       </c>
-      <c r="J199" t="inlineStr">
+      <c r="K199" t="inlineStr">
         <is>
           <t>Antanimandry Health Centre</t>
         </is>
       </c>
-      <c r="K199" t="n">
+      <c r="L199" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -9977,24 +10521,31 @@
         <v>2146</v>
       </c>
       <c r="E200" t="n">
+        <v>1441</v>
+      </c>
+      <c r="F200" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
         <v>1716</v>
       </c>
-      <c r="F200" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="n">
+      <c r="I200" t="n">
         <v>292</v>
       </c>
-      <c r="I200" t="n">
+      <c r="J200" t="n">
         <v>2.4</v>
       </c>
-      <c r="J200" t="inlineStr">
+      <c r="K200" t="inlineStr">
         <is>
           <t>Masiniloharano Health Centre</t>
         </is>
       </c>
-      <c r="K200" t="n">
+      <c r="L200" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -10018,28 +10569,31 @@
         <v>783</v>
       </c>
       <c r="E201" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F201" t="n">
+        <v>65</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
         <v>1497</v>
       </c>
-      <c r="F201" t="n">
-        <v>91</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H201" t="n">
+      <c r="I201" t="n">
         <v>254</v>
       </c>
-      <c r="I201" t="n">
+      <c r="J201" t="n">
         <v>2.1</v>
       </c>
-      <c r="J201" t="inlineStr">
+      <c r="K201" t="inlineStr">
         <is>
           <t>Antanimandry Health Centre</t>
         </is>
       </c>
-      <c r="K201" t="n">
+      <c r="L201" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -10063,28 +10617,27 @@
         <v>998</v>
       </c>
       <c r="E202" t="n">
+        <v>1277</v>
+      </c>
+      <c r="F202" t="n">
+        <v>28</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="n">
         <v>1480</v>
       </c>
-      <c r="F202" t="n">
-        <v>48</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H202" t="n">
+      <c r="I202" t="n">
         <v>252</v>
       </c>
-      <c r="I202" t="n">
+      <c r="J202" t="n">
         <v>2.1</v>
       </c>
-      <c r="J202" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>Marofangady Health Post</t>
         </is>
       </c>
-      <c r="K202" t="n">
+      <c r="L202" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -10108,24 +10661,27 @@
         <v>1476</v>
       </c>
       <c r="E203" t="n">
-        <v>1471</v>
+        <v>1216</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="n">
+        <v>1471</v>
+      </c>
+      <c r="I203" t="n">
         <v>250</v>
       </c>
-      <c r="I203" t="n">
+      <c r="J203" t="n">
         <v>2.1</v>
       </c>
-      <c r="J203" t="inlineStr">
+      <c r="K203" t="inlineStr">
         <is>
           <t>Antanimandry Health Centre</t>
         </is>
       </c>
-      <c r="K203" t="n">
+      <c r="L203" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -10149,24 +10705,27 @@
         <v>1399</v>
       </c>
       <c r="E204" t="n">
-        <v>1471</v>
+        <v>1286</v>
       </c>
       <c r="F204" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="n">
+        <v>1471</v>
+      </c>
+      <c r="I204" t="n">
         <v>250</v>
       </c>
-      <c r="I204" t="n">
+      <c r="J204" t="n">
         <v>2.1</v>
       </c>
-      <c r="J204" t="inlineStr">
+      <c r="K204" t="inlineStr">
         <is>
           <t>Antanimandry Health Centre</t>
         </is>
       </c>
-      <c r="K204" t="n">
+      <c r="L204" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -10190,29 +10749,32 @@
         <v>1235</v>
       </c>
       <c r="E205" t="n">
-        <v>1437</v>
+        <v>1248</v>
       </c>
       <c r="F205" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="n">
+        <v>1437</v>
+      </c>
+      <c r="I205" t="n">
         <v>244</v>
       </c>
-      <c r="I205" t="n">
+      <c r="J205" t="n">
         <v>2</v>
       </c>
-      <c r="J205" t="inlineStr">
+      <c r="K205" t="inlineStr">
         <is>
           <t>Antanimandry Health Centre</t>
         </is>
       </c>
-      <c r="K205" t="n">
+      <c r="L205" t="n">
         <v>0.9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K205"/>
+  <autoFilter ref="A1:L205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
